--- a/BOM/Lineux Stealth Tiga Bom.xlsx
+++ b/BOM/Lineux Stealth Tiga Bom.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="72">
   <si>
     <t>Lineux Stealth Tiga Bill Of Material</t>
   </si>
@@ -67,6 +67,9 @@
     <t>including 3 for sherpa micro toolboard mount. other extruders may differ</t>
   </si>
   <si>
+    <t>including 2 for eddy</t>
+  </si>
+  <si>
     <t>m3 x 6mm bhcs</t>
   </si>
   <si>
@@ -83,6 +86,9 @@
   </si>
   <si>
     <t>including 2 for sherpa micro base mount. other extruders may differ</t>
+  </si>
+  <si>
+    <t>m3 x 12mm bhcs</t>
   </si>
   <si>
     <t>m3 x 20mm shcs</t>
@@ -1027,13 +1033,15 @@
         <v>16</v>
       </c>
       <c r="B11" s="17">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="C11" s="18" t="s">
         <v>17</v>
       </c>
       <c r="D11" s="4"/>
-      <c r="E11" s="10"/>
+      <c r="E11" s="19" t="s">
+        <v>18</v>
+      </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
@@ -1058,7 +1066,7 @@
     </row>
     <row r="12">
       <c r="A12" s="20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="17">
         <v>4.0</v>
@@ -1066,7 +1074,7 @@
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -1092,7 +1100,7 @@
     </row>
     <row r="13">
       <c r="A13" s="20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="17">
         <v>4.0</v>
@@ -1100,7 +1108,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
@@ -1126,13 +1134,13 @@
     </row>
     <row r="14">
       <c r="A14" s="20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" s="17">
         <v>3.0</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="19"/>
@@ -1160,12 +1168,14 @@
     </row>
     <row r="15">
       <c r="A15" s="20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="17">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="18" t="s">
+        <v>18</v>
+      </c>
       <c r="D15" s="4"/>
       <c r="E15" s="10"/>
       <c r="F15" s="4"/>
@@ -1192,16 +1202,14 @@
     </row>
     <row r="16">
       <c r="A16" s="20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" s="17">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="19" t="s">
-        <v>26</v>
-      </c>
+      <c r="E16" s="10"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
@@ -1229,13 +1237,13 @@
         <v>27</v>
       </c>
       <c r="B17" s="17">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="19"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
@@ -1259,15 +1267,17 @@
       <c r="Z17" s="4"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="20" t="s">
         <v>29</v>
       </c>
       <c r="B18" s="17">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
-      <c r="C18" s="4"/>
+      <c r="C18" s="18" t="s">
+        <v>30</v>
+      </c>
       <c r="D18" s="4"/>
-      <c r="E18" s="10"/>
+      <c r="E18" s="19"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -1292,10 +1302,10 @@
     </row>
     <row r="19">
       <c r="A19" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" s="17">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -1324,7 +1334,7 @@
     </row>
     <row r="20">
       <c r="A20" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B20" s="17">
         <v>4.0</v>
@@ -1356,15 +1366,13 @@
     </row>
     <row r="21">
       <c r="A21" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21" s="17">
         <v>4.0</v>
       </c>
       <c r="C21" s="4"/>
-      <c r="D21" s="21" t="s">
-        <v>33</v>
-      </c>
+      <c r="D21" s="4"/>
       <c r="E21" s="10"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
@@ -1389,16 +1397,16 @@
       <c r="Z21" s="4"/>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="9" t="s">
         <v>34</v>
       </c>
       <c r="B22" s="17">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="4"/>
+      <c r="D22" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="21"/>
       <c r="E22" s="10"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
@@ -1429,7 +1437,9 @@
       <c r="B23" s="17">
         <v>1.0</v>
       </c>
-      <c r="C23" s="4"/>
+      <c r="C23" s="18" t="s">
+        <v>37</v>
+      </c>
       <c r="D23" s="21"/>
       <c r="E23" s="10"/>
       <c r="F23" s="4"/>
@@ -1455,17 +1465,15 @@
       <c r="Z23" s="4"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="s">
-        <v>37</v>
+      <c r="A24" s="20" t="s">
+        <v>38</v>
       </c>
       <c r="B24" s="17">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="19" t="s">
-        <v>38</v>
-      </c>
+      <c r="D24" s="21"/>
+      <c r="E24" s="10"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
@@ -1493,11 +1501,13 @@
         <v>39</v>
       </c>
       <c r="B25" s="17">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
-      <c r="E25" s="10"/>
+      <c r="E25" s="19" t="s">
+        <v>40</v>
+      </c>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
@@ -1522,15 +1532,13 @@
     </row>
     <row r="26">
       <c r="A26" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B26" s="17">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="C26" s="4"/>
-      <c r="D26" s="21" t="s">
-        <v>33</v>
-      </c>
+      <c r="D26" s="4"/>
       <c r="E26" s="10"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -1556,14 +1564,14 @@
     </row>
     <row r="27">
       <c r="A27" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B27" s="17">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="21" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E27" s="10"/>
       <c r="F27" s="4"/>
@@ -1590,16 +1598,14 @@
     </row>
     <row r="28">
       <c r="A28" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B28" s="17">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
-      <c r="C28" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="D28" s="22" t="s">
-        <v>33</v>
+      <c r="C28" s="4"/>
+      <c r="D28" s="21" t="s">
+        <v>35</v>
       </c>
       <c r="E28" s="10"/>
       <c r="F28" s="4"/>
@@ -1625,7 +1631,7 @@
       <c r="Z28" s="4"/>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="9" t="s">
         <v>44</v>
       </c>
       <c r="B29" s="17">
@@ -1634,7 +1640,9 @@
       <c r="C29" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D29" s="23"/>
+      <c r="D29" s="22" t="s">
+        <v>35</v>
+      </c>
       <c r="E29" s="10"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -1665,10 +1673,10 @@
       <c r="B30" s="17">
         <v>1.0</v>
       </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="22" t="s">
-        <v>33</v>
+      <c r="C30" s="18" t="s">
+        <v>47</v>
       </c>
+      <c r="D30" s="23"/>
       <c r="E30" s="10"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
@@ -1693,15 +1701,15 @@
       <c r="Z30" s="4"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="s">
-        <v>47</v>
+      <c r="A31" s="20" t="s">
+        <v>48</v>
       </c>
       <c r="B31" s="17">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="C31" s="4"/>
-      <c r="D31" s="21" t="s">
-        <v>33</v>
+      <c r="D31" s="22" t="s">
+        <v>35</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="4"/>
@@ -1728,18 +1736,16 @@
     </row>
     <row r="32">
       <c r="A32" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B32" s="17">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
-      <c r="C32" s="22" t="s">
-        <v>49</v>
+      <c r="C32" s="4"/>
+      <c r="D32" s="21" t="s">
+        <v>35</v>
       </c>
-      <c r="D32" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="E32" s="24"/>
+      <c r="E32" s="10"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
@@ -1763,11 +1769,19 @@
       <c r="Z32" s="4"/>
     </row>
     <row r="33">
-      <c r="A33" s="25"/>
-      <c r="B33" s="26"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="27"/>
+      <c r="A33" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E33" s="24"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
@@ -1791,21 +1805,11 @@
       <c r="Z33" s="4"/>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>12</v>
-      </c>
+      <c r="A34" s="25"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="27"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
@@ -1829,15 +1833,21 @@
       <c r="Z34" s="4"/>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="s">
-        <v>13</v>
+      <c r="A35" s="13" t="s">
+        <v>52</v>
       </c>
-      <c r="B35" s="17">
-        <v>4.0</v>
+      <c r="B35" s="14" t="s">
+        <v>9</v>
       </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="10"/>
+      <c r="C35" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>12</v>
+      </c>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
@@ -1862,10 +1872,10 @@
     </row>
     <row r="36">
       <c r="A36" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B36" s="17">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -1894,10 +1904,10 @@
     </row>
     <row r="37">
       <c r="A37" s="9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B37" s="17">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -1926,10 +1936,10 @@
     </row>
     <row r="38">
       <c r="A38" s="9" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="B38" s="17">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -1958,10 +1968,10 @@
     </row>
     <row r="39">
       <c r="A39" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B39" s="17">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -1990,10 +2000,10 @@
     </row>
     <row r="40">
       <c r="A40" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B40" s="17">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -2022,15 +2032,13 @@
     </row>
     <row r="41">
       <c r="A41" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B41" s="17">
         <v>4.0</v>
       </c>
       <c r="C41" s="4"/>
-      <c r="D41" s="21" t="s">
-        <v>33</v>
-      </c>
+      <c r="D41" s="4"/>
       <c r="E41" s="10"/>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
@@ -2055,14 +2063,16 @@
       <c r="Z41" s="4"/>
     </row>
     <row r="42">
-      <c r="A42" s="20" t="s">
-        <v>55</v>
+      <c r="A42" s="9" t="s">
+        <v>56</v>
       </c>
       <c r="B42" s="17">
         <v>4.0</v>
       </c>
       <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
+      <c r="D42" s="21" t="s">
+        <v>35</v>
+      </c>
       <c r="E42" s="10"/>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
@@ -2087,11 +2097,11 @@
       <c r="Z42" s="4"/>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="s">
-        <v>39</v>
+      <c r="A43" s="20" t="s">
+        <v>57</v>
       </c>
       <c r="B43" s="17">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -2120,15 +2130,13 @@
     </row>
     <row r="44">
       <c r="A44" s="9" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B44" s="17">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="C44" s="4"/>
-      <c r="D44" s="21" t="s">
-        <v>33</v>
-      </c>
+      <c r="D44" s="4"/>
       <c r="E44" s="10"/>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
@@ -2154,16 +2162,14 @@
     </row>
     <row r="45">
       <c r="A45" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B45" s="17">
         <v>1.0</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>58</v>
-      </c>
+      <c r="C45" s="4"/>
       <c r="D45" s="21" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E45" s="10"/>
       <c r="F45" s="4"/>
@@ -2198,8 +2204,8 @@
       <c r="C46" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="22" t="s">
-        <v>33</v>
+      <c r="D46" s="21" t="s">
+        <v>35</v>
       </c>
       <c r="E46" s="10"/>
       <c r="F46" s="4"/>
@@ -2234,8 +2240,8 @@
       <c r="C47" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D47" s="21" t="s">
-        <v>33</v>
+      <c r="D47" s="22" t="s">
+        <v>35</v>
       </c>
       <c r="E47" s="10"/>
       <c r="F47" s="4"/>
@@ -2261,19 +2267,19 @@
       <c r="Z47" s="4"/>
     </row>
     <row r="48">
-      <c r="A48" s="20" t="s">
+      <c r="A48" s="9" t="s">
         <v>63</v>
       </c>
       <c r="B48" s="17">
         <v>1.0</v>
       </c>
-      <c r="C48" s="18"/>
-      <c r="D48" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="E48" s="19" t="s">
+      <c r="C48" s="4" t="s">
         <v>64</v>
       </c>
+      <c r="D48" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E48" s="10"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
@@ -2297,11 +2303,19 @@
       <c r="Z48" s="4"/>
     </row>
     <row r="49">
-      <c r="A49" s="25"/>
-      <c r="B49" s="26"/>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="27"/>
+      <c r="A49" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B49" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="C49" s="18"/>
+      <c r="D49" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>66</v>
+      </c>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
@@ -2325,21 +2339,11 @@
       <c r="Z49" s="4"/>
     </row>
     <row r="50">
-      <c r="A50" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="B50" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C50" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="16" t="s">
-        <v>12</v>
-      </c>
+      <c r="A50" s="25"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="27"/>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
@@ -2363,17 +2367,21 @@
       <c r="Z50" s="4"/>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B51" s="29">
-        <v>1.0</v>
-      </c>
-      <c r="C51" s="4" t="s">
+      <c r="A51" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="D51" s="4"/>
-      <c r="E51" s="10"/>
+      <c r="B51" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="16" t="s">
+        <v>12</v>
+      </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -2404,12 +2412,10 @@
         <v>1.0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D52" s="4"/>
-      <c r="E52" s="10" t="s">
-        <v>69</v>
-      </c>
+      <c r="E52" s="10"/>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
@@ -2433,11 +2439,19 @@
       <c r="Z52" s="4"/>
     </row>
     <row r="53">
-      <c r="A53" s="25"/>
-      <c r="B53" s="26"/>
-      <c r="C53" s="26"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="27"/>
+      <c r="A53" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B53" s="29">
+        <v>1.0</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D53" s="4"/>
+      <c r="E53" s="10" t="s">
+        <v>71</v>
+      </c>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -2461,11 +2475,11 @@
       <c r="Z53" s="4"/>
     </row>
     <row r="54">
-      <c r="A54" s="4"/>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
+      <c r="A54" s="25"/>
+      <c r="B54" s="26"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="27"/>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
@@ -28360,6 +28374,34 @@
       <c r="Y978" s="4"/>
       <c r="Z978" s="4"/>
     </row>
+    <row r="979">
+      <c r="A979" s="4"/>
+      <c r="B979" s="4"/>
+      <c r="C979" s="4"/>
+      <c r="D979" s="4"/>
+      <c r="E979" s="4"/>
+      <c r="F979" s="4"/>
+      <c r="G979" s="4"/>
+      <c r="H979" s="4"/>
+      <c r="I979" s="4"/>
+      <c r="J979" s="4"/>
+      <c r="K979" s="4"/>
+      <c r="L979" s="4"/>
+      <c r="M979" s="4"/>
+      <c r="N979" s="4"/>
+      <c r="O979" s="4"/>
+      <c r="P979" s="4"/>
+      <c r="Q979" s="4"/>
+      <c r="R979" s="4"/>
+      <c r="S979" s="4"/>
+      <c r="T979" s="4"/>
+      <c r="U979" s="4"/>
+      <c r="V979" s="4"/>
+      <c r="W979" s="4"/>
+      <c r="X979" s="4"/>
+      <c r="Y979" s="4"/>
+      <c r="Z979" s="4"/>
+    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:E1"/>
@@ -28372,20 +28414,20 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B7"/>
-    <hyperlink r:id="rId2" ref="D21"/>
-    <hyperlink r:id="rId3" ref="D26"/>
-    <hyperlink r:id="rId4" ref="D27"/>
-    <hyperlink r:id="rId5" ref="D28"/>
-    <hyperlink r:id="rId6" ref="D30"/>
-    <hyperlink r:id="rId7" ref="D31"/>
-    <hyperlink r:id="rId8" ref="C32"/>
-    <hyperlink r:id="rId9" ref="D32"/>
-    <hyperlink r:id="rId10" ref="D41"/>
-    <hyperlink r:id="rId11" ref="D44"/>
-    <hyperlink r:id="rId12" ref="D45"/>
-    <hyperlink r:id="rId13" ref="D46"/>
-    <hyperlink r:id="rId14" ref="D47"/>
-    <hyperlink r:id="rId15" ref="D48"/>
+    <hyperlink r:id="rId2" ref="D22"/>
+    <hyperlink r:id="rId3" ref="D27"/>
+    <hyperlink r:id="rId4" ref="D28"/>
+    <hyperlink r:id="rId5" ref="D29"/>
+    <hyperlink r:id="rId6" ref="D31"/>
+    <hyperlink r:id="rId7" ref="D32"/>
+    <hyperlink r:id="rId8" ref="C33"/>
+    <hyperlink r:id="rId9" ref="D33"/>
+    <hyperlink r:id="rId10" ref="D42"/>
+    <hyperlink r:id="rId11" ref="D45"/>
+    <hyperlink r:id="rId12" ref="D46"/>
+    <hyperlink r:id="rId13" ref="D47"/>
+    <hyperlink r:id="rId14" ref="D48"/>
+    <hyperlink r:id="rId15" ref="D49"/>
   </hyperlinks>
   <drawing r:id="rId16"/>
 </worksheet>
